--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487922_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487922_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.152200000000001</v>
+        <v>9.6372</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1013</v>
+        <v>9.3809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0508</v>
+        <v>0.2564</v>
       </c>
       <c r="G2" t="n">
         <v>2.8699</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2297</v>
+        <v>0.2554</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5905</v>
+        <v>-0.3109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3608</v>
+        <v>0.5663</v>
       </c>
       <c r="V2" t="n">
         <v>4.847</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.0121</v>
+        <v>8.2608</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2646</v>
+        <v>5.8656</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7475</v>
+        <v>2.3952</v>
       </c>
       <c r="G3" t="n">
         <v>4.3563</v>
@@ -688,13 +688,13 @@
         <v>3.3299</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0013</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9663</v>
+        <v>-0.3652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9676</v>
+        <v>0.6153</v>
       </c>
       <c r="V3" t="n">
         <v>2.4058</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9001</v>
+        <v>1.0432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0518</v>
+        <v>0.2242</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="G4" t="n">
         <v>0.357</v>
@@ -766,13 +766,13 @@
         <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3706</v>
+        <v>-0.2275</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5748</v>
+        <v>-0.4024</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2042</v>
+        <v>0.1749</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1675</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0914</v>
+        <v>-0.2682</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6654</v>
+        <v>0.1296</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.574</v>
+        <v>-0.3978</v>
       </c>
       <c r="G5" t="n">
         <v>0.735</v>
@@ -844,13 +844,13 @@
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.2236</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3849</v>
+        <v>-0.1509</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1984</v>
+        <v>0.3745</v>
       </c>
       <c r="V5" t="n">
         <v>0.23</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3296</v>
+        <v>-0.5858</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5462</v>
+        <v>-0.8024</v>
       </c>
       <c r="F6" t="n">
         <v>0.2166</v>
@@ -922,10 +922,10 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5063</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4658</v>
+        <v>0.2096</v>
       </c>
       <c r="U6" t="n">
         <v>0.0405</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.299</v>
+        <v>-1.114</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0125</v>
+        <v>0.2018</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2864</v>
+        <v>-1.3158</v>
       </c>
       <c r="G7" t="n">
         <v>0.9659</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.473</v>
+        <v>-0.288</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0815</v>
+        <v>-0.1109</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6681</v>
+        <v>-2.4957</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5624</v>
+        <v>-2.39</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1056</v>
@@ -1078,10 +1078,10 @@
         <v>2.9137</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3634</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1866</v>
+        <v>-0.0142</v>
       </c>
       <c r="U8" t="n">
         <v>0.55</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0315</v>
+        <v>-3.0902</v>
       </c>
       <c r="E9" t="n">
         <v>-0.6958</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3357</v>
+        <v>-2.3944</v>
       </c>
       <c r="G9" t="n">
         <v>-1.586</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3373</v>
+        <v>-0.396</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1416</v>
+        <v>-0.2003</v>
       </c>
       <c r="V9" t="n">
         <v>-2.565</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3942</v>
+        <v>-5.6276</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2272</v>
+        <v>-3.5486</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1671</v>
+        <v>-2.079</v>
       </c>
       <c r="G10" t="n">
         <v>-5.157</v>
@@ -1234,13 +1234,13 @@
         <v>3.1218</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7326</v>
+        <v>0.4992</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2668</v>
+        <v>-0.0547</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4659</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0.0708</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.433399999999999</v>
+        <v>5.759699999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>8.039000000000001</v>
+        <v>8.365300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.605599999999999</v>
+        <v>-2.6054</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7143</v>
@@ -1312,13 +1312,13 @@
         <v>20.8118</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7762000000000001</v>
+        <v>1.1025</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7879</v>
+        <v>-1.4615</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5643</v>
+        <v>2.5642</v>
       </c>
       <c r="V11" t="n">
         <v>2.0875</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9184</v>
+        <v>4.7804</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1031</v>
+        <v>4.3174</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8153</v>
+        <v>0.463</v>
       </c>
       <c r="G12" t="n">
         <v>2.4607</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5233</v>
+        <v>0.3853</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6929</v>
+        <v>-0.4786</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2162</v>
+        <v>0.8639</v>
       </c>
       <c r="V12" t="n">
         <v>0.4776</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6964</v>
+        <v>4.1353</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4644</v>
+        <v>6.7859</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7681</v>
+        <v>-2.6506</v>
       </c>
       <c r="G13" t="n">
         <v>5.0777</v>
@@ -1468,13 +1468,13 @@
         <v>1.2487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1951</v>
+        <v>0.2438</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3791</v>
+        <v>-0.0576</v>
       </c>
       <c r="U13" t="n">
-        <v>0.184</v>
+        <v>0.3014</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3538</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8876</v>
+        <v>3.1377</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0662</v>
+        <v>4.1734</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1786</v>
+        <v>-1.0357</v>
       </c>
       <c r="G14" t="n">
         <v>4.4404</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9877</v>
+        <v>-0.7377</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.64</v>
+        <v>-0.5329</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3477</v>
+        <v>-0.2048</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3975</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9953</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7905</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1857</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0.423</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.137</v>
+        <v>0.1561</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2675</v>
+        <v>0.1794</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4798</v>
+        <v>0.2297</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4578</v>
+        <v>1.6721</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9376</v>
+        <v>-1.4424</v>
       </c>
       <c r="G16" t="n">
         <v>0.8232</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2624</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.64</v>
+        <v>-0.4257</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6224</v>
+        <v>-0.1272</v>
       </c>
       <c r="V16" t="n">
         <v>0.5838</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0753</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9614</v>
+        <v>-0.8542</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1139</v>
+        <v>0.2932</v>
       </c>
       <c r="G17" t="n">
         <v>0.0501</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5011</v>
+        <v>0.0132</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1096</v>
+        <v>0.2975</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0952</v>
+        <v>-1.0467</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1326</v>
+        <v>0.2398</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2278</v>
+        <v>-1.2865</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8726</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.182</v>
+        <v>-0.1336</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1442</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5025</v>
+        <v>-2.112</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3101</v>
+        <v>-0.0958</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1924</v>
+        <v>-2.0162</v>
       </c>
       <c r="G19" t="n">
         <v>0.5825</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.625</v>
+        <v>-0.2345</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3791</v>
+        <v>-0.1648</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2459</v>
+        <v>-0.0698</v>
       </c>
       <c r="V19" t="n">
         <v>-1.6275</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7677</v>
+        <v>-2.5916</v>
       </c>
       <c r="E20" t="n">
         <v>-3.1911</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4234</v>
+        <v>0.5996</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6488</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4945</v>
+        <v>-0.3184</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1833</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3112</v>
+        <v>-0.135</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4002</v>
+        <v>-5.5168</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5842</v>
+        <v>-4.2272</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-1.2897</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1631</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8816</v>
+        <v>0.765</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6582</v>
+        <v>0.0153</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2233</v>
+        <v>0.7497</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5915</v>
+        <v>-6.1693</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3623</v>
+        <v>-7.1124</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7709</v>
+        <v>0.9431</v>
       </c>
       <c r="G22" t="n">
         <v>-5.4587</v>
@@ -2170,13 +2170,13 @@
         <v>2.2893</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9297</v>
+        <v>0.3518</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5401</v>
+        <v>-0.21</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3896</v>
+        <v>0.5618</v>
       </c>
       <c r="V22" t="n">
         <v>-0.23</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.433499999999999</v>
+        <v>-4.718999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6055</v>
+        <v>2.605600000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.039100000000001</v>
+        <v>-7.324600000000001</v>
       </c>
       <c r="G23" t="n">
         <v>4.714400000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.5276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7762</v>
+        <v>-0.06190000000000007</v>
       </c>
       <c r="T23" t="n">
         <v>-2.5643</v>
       </c>
       <c r="U23" t="n">
-        <v>1.788</v>
+        <v>2.5024</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0875</v>
